--- a/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2015_2026/tabelas/diagnosticos_residuos.xlsx
+++ b/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2015_2026/tabelas/diagnosticos_residuos.xlsx
@@ -485,16 +485,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>535.3220478601634</v>
+        <v>535.3220478601631</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001366536128969604</v>
+        <v>0.00136653612896963</v>
       </c>
       <c r="E2" t="n">
-        <v>169.9412671941751</v>
+        <v>169.8402146478741</v>
       </c>
       <c r="F2" t="n">
-        <v>7.037199512166816e-29</v>
+        <v>7.375854335016048e-29</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -523,16 +523,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>8.285631933106558</v>
+        <v>8.285631933106417</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1411806097972043</v>
+        <v>0.1411806097972111</v>
       </c>
       <c r="J3" t="n">
-        <v>1.224744251730816</v>
+        <v>1.224744251730806</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3044140111263073</v>
+        <v>0.3044140111263121</v>
       </c>
     </row>
     <row r="4">
@@ -562,10 +562,10 @@
         <v>0.4602252754830636</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6665696509706533</v>
+        <v>0.666569650970656</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6497968381665387</v>
+        <v>0.6497968381665367</v>
       </c>
     </row>
     <row r="5">
@@ -589,16 +589,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.718153737197091</v>
+        <v>2.718153737197147</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7433405344600156</v>
+        <v>0.743340534460007</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3836402232848423</v>
+        <v>0.3836402232848508</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8587710264345523</v>
+        <v>0.8587710264345465</v>
       </c>
     </row>
     <row r="6">
@@ -628,10 +628,10 @@
         <v>0.4437814412954527</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6855781286985256</v>
+        <v>0.6855781286985334</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6356047026199276</v>
+        <v>0.6356047026199223</v>
       </c>
     </row>
     <row r="7">
@@ -651,20 +651,20 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>12.10737444279923</v>
+        <v>8.051489467485004</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03334575826523875</v>
+        <v>0.1534206788725819</v>
       </c>
       <c r="J7" t="n">
-        <v>1.849709884850297</v>
+        <v>1.187771817564571</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1115421722494569</v>
+        <v>0.321818274903742</v>
       </c>
     </row>
     <row r="8">
@@ -684,20 +684,20 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>8.051489467485045</v>
+        <v>12.10737444279912</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1534206788725799</v>
+        <v>0.03334575826524024</v>
       </c>
       <c r="J8" t="n">
-        <v>1.187771817564582</v>
+        <v>1.849709884850265</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3218182749037364</v>
+        <v>0.1115421722494628</v>
       </c>
     </row>
     <row r="9">
@@ -721,16 +721,16 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.619382191100637</v>
+        <v>6.619382191100622</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2505205155397817</v>
+        <v>0.2505205155397826</v>
       </c>
       <c r="J9" t="n">
-        <v>0.964790199942866</v>
+        <v>0.9647901999428676</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4439508531400205</v>
+        <v>0.4439508531400197</v>
       </c>
     </row>
     <row r="10">
@@ -745,16 +745,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>518.369730443962</v>
+        <v>518.3697304439621</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006407425489018732</v>
+        <v>0.006407425489018663</v>
       </c>
       <c r="E10" t="n">
-        <v>198.9410250397006</v>
+        <v>199.1299268916917</v>
       </c>
       <c r="F10" t="n">
-        <v>9.037890486539637e-35</v>
+        <v>8.269795930526075e-35</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8.343986238869212</v>
+        <v>8.343986238869171</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1382691738110988</v>
+        <v>0.1382691738111014</v>
       </c>
       <c r="J11" t="n">
-        <v>1.233981637785929</v>
+        <v>1.233981637785931</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3001884912521912</v>
+        <v>0.3001884912521903</v>
       </c>
     </row>
     <row r="12">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.615617311373596</v>
+        <v>2.615617311373554</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7589910024592351</v>
+        <v>0.7589910024592414</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3688614411821832</v>
+        <v>0.3688614411821837</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8686586391383919</v>
+        <v>0.8686586391383917</v>
       </c>
     </row>
     <row r="13">
@@ -849,16 +849,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3.312311054376831</v>
+        <v>3.312311054376775</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6519573997031533</v>
+        <v>0.6519573997031618</v>
       </c>
       <c r="J13" t="n">
-        <v>0.469763615579237</v>
+        <v>0.4697636155792343</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7978187208836226</v>
+        <v>0.7978187208836247</v>
       </c>
     </row>
     <row r="14">
@@ -882,16 +882,16 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3.165798802591302</v>
+        <v>3.1657988025914</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6744419066418693</v>
+        <v>0.6744419066418544</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4484491992304521</v>
+        <v>0.448449199230452</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8133376130566197</v>
+        <v>0.8133376130566198</v>
       </c>
     </row>
     <row r="15">
@@ -911,20 +911,20 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6.208042332372676</v>
+        <v>2.48833410042757</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2864986733751507</v>
+        <v>0.7782509448843075</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9017294540172263</v>
+        <v>0.3505499908214773</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4838165523772481</v>
+        <v>0.8806112345771839</v>
       </c>
     </row>
     <row r="16">
@@ -944,20 +944,20 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2.488334100427626</v>
+        <v>6.208042332372703</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7782509448842991</v>
+        <v>0.2864986733751481</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3505499908214814</v>
+        <v>0.9017294540172329</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8806112345771813</v>
+        <v>0.483816552377244</v>
       </c>
     </row>
     <row r="17">
@@ -981,16 +981,16 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.043035957551387</v>
+        <v>2.043035957551359</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8431587247015317</v>
+        <v>0.8431587247015356</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2867836102312167</v>
+        <v>0.2867836102312148</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9191536483776778</v>
+        <v>0.919153648377679</v>
       </c>
     </row>
     <row r="18">
@@ -1005,16 +1005,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>524.1375665055995</v>
+        <v>524.1375665055989</v>
       </c>
       <c r="D18" t="n">
-        <v>0.003875642892129501</v>
+        <v>0.003875642892129703</v>
       </c>
       <c r="E18" t="n">
-        <v>444.5436025537371</v>
+        <v>444.7727761081053</v>
       </c>
       <c r="F18" t="n">
-        <v>5.062747024999954e-86</v>
+        <v>4.52854476603128e-86</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1043,16 +1043,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>10.12057410080606</v>
+        <v>10.1205741008061</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07189003667083242</v>
+        <v>0.07189003667083124</v>
       </c>
       <c r="J19" t="n">
-        <v>1.519665704136444</v>
+        <v>1.519665704136452</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1919852700948363</v>
+        <v>0.1919852700948337</v>
       </c>
     </row>
     <row r="20">
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.322044933879915</v>
+        <v>1.322044933879887</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9326470070069302</v>
+        <v>0.932647007006933</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1845040034327696</v>
+        <v>0.1845040034327691</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9677591863217578</v>
+        <v>0.9677591863217581</v>
       </c>
     </row>
     <row r="21">
@@ -1109,16 +1109,16 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.026982950213393</v>
+        <v>5.026982950213364</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4125960401475334</v>
+        <v>0.4125960401475373</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7230496970883484</v>
+        <v>0.7230496970883495</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6079209488606055</v>
+        <v>0.6079209488606054</v>
       </c>
     </row>
     <row r="22">
@@ -1142,16 +1142,16 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5.989766925346386</v>
+        <v>5.98976692534647</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3072159150805087</v>
+        <v>0.3072159150805007</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8684421472308607</v>
+        <v>0.8684421472308606</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5057542197389494</v>
+        <v>0.5057542197389492</v>
       </c>
     </row>
     <row r="23">
@@ -1171,20 +1171,20 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>10.66923291827688</v>
+        <v>6.820109259982493</v>
       </c>
       <c r="I23" t="n">
-        <v>0.05834717558078709</v>
+        <v>0.2343664666322685</v>
       </c>
       <c r="J23" t="n">
-        <v>1.609671534105637</v>
+        <v>0.9957208417195581</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1659486574097769</v>
+        <v>0.4252381512940118</v>
       </c>
     </row>
     <row r="24">
@@ -1204,20 +1204,20 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.820109259982646</v>
+        <v>10.66923291827688</v>
       </c>
       <c r="I24" t="n">
-        <v>0.234366466632257</v>
+        <v>0.05834717558078709</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9957208417195845</v>
+        <v>1.609671534105639</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4252381512939963</v>
+        <v>0.1659486574097762</v>
       </c>
     </row>
     <row r="25">
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.830770891802198</v>
+        <v>6.830770891802044</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2335333935660506</v>
+        <v>0.2335333935660631</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9973666390796672</v>
+        <v>0.9973666390796417</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4242582734335928</v>
+        <v>0.4242582734336083</v>
       </c>
     </row>
     <row r="26">
@@ -1265,16 +1265,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>500.3957870017568</v>
+        <v>500.3957870017577</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02626068287276134</v>
+        <v>0.02626068287275959</v>
       </c>
       <c r="E26" t="n">
-        <v>397.8805212275226</v>
+        <v>397.5030780239355</v>
       </c>
       <c r="F26" t="n">
-        <v>3.544677679827491e-76</v>
+        <v>4.256739725484979e-76</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1303,16 +1303,16 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>7.618309589238872</v>
+        <v>7.618309589238802</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1785638781794382</v>
+        <v>0.1785638781794424</v>
       </c>
       <c r="J27" t="n">
-        <v>1.119755820286083</v>
+        <v>1.119755820286078</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3559269216363763</v>
+        <v>0.3559269216363789</v>
       </c>
     </row>
     <row r="28">
@@ -1342,10 +1342,10 @@
         <v>0.9872453696571164</v>
       </c>
       <c r="J28" t="n">
-        <v>0.08552469282718726</v>
+        <v>0.08552469282718608</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9943448682358992</v>
+        <v>0.9943448682358993</v>
       </c>
     </row>
     <row r="29">
@@ -1369,16 +1369,16 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6.58683154684941</v>
+        <v>6.586831546849313</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2532252536379183</v>
+        <v>0.2532252536379262</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9597841712084314</v>
+        <v>0.9597841712084216</v>
       </c>
       <c r="K29" t="n">
-        <v>0.4470321704819782</v>
+        <v>0.447032170481984</v>
       </c>
     </row>
     <row r="30">
@@ -1408,10 +1408,10 @@
         <v>0.5598479130991525</v>
       </c>
       <c r="J30" t="n">
-        <v>0.559872505650754</v>
+        <v>0.5598725056507564</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7304277061089275</v>
+        <v>0.7304277061089255</v>
       </c>
     </row>
     <row r="31">
@@ -1431,20 +1431,20 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.759331082409254</v>
+        <v>6.605161578794919</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7370301254247773</v>
+        <v>0.2516991977067485</v>
       </c>
       <c r="J31" t="n">
-        <v>0.389582118107666</v>
+        <v>0.9626028477510766</v>
       </c>
       <c r="K31" t="n">
-        <v>0.85473957372868</v>
+        <v>0.4452954192285794</v>
       </c>
     </row>
     <row r="32">
@@ -1464,20 +1464,20 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6.605161578794835</v>
+        <v>2.759331082409282</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2516991977067553</v>
+        <v>0.737030125424773</v>
       </c>
       <c r="J32" t="n">
-        <v>0.9626028477510609</v>
+        <v>0.389582118107669</v>
       </c>
       <c r="K32" t="n">
-        <v>0.4452954192285886</v>
+        <v>0.854739573728678</v>
       </c>
     </row>
     <row r="33">
@@ -1501,16 +1501,16 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>11.59929990804855</v>
+        <v>11.59929990804858</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04071052578663077</v>
+        <v>0.04071052578663031</v>
       </c>
       <c r="J33" t="n">
-        <v>1.764218385357985</v>
+        <v>1.764218385357984</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1286597895399987</v>
+        <v>0.128659789539999</v>
       </c>
     </row>
     <row r="34">
@@ -1525,16 +1525,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>531.1907990426604</v>
+        <v>531.1907990426602</v>
       </c>
       <c r="D34" t="n">
-        <v>0.002029115468245141</v>
+        <v>0.002029115468245184</v>
       </c>
       <c r="E34" t="n">
-        <v>192.0938127659443</v>
+        <v>192.9867644018773</v>
       </c>
       <c r="F34" t="n">
-        <v>2.25230407047717e-33</v>
+        <v>1.481423068966235e-33</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -1563,16 +1563,16 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>7.554519140808547</v>
+        <v>7.554519140808477</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1825562884760598</v>
+        <v>0.1825562884760639</v>
       </c>
       <c r="J35" t="n">
-        <v>1.109781750190501</v>
+        <v>1.10978175019049</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3611596298702544</v>
+        <v>0.3611596298702604</v>
       </c>
     </row>
     <row r="36">
@@ -1602,7 +1602,7 @@
         <v>0.6213158292007928</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4991444801979904</v>
+        <v>0.4991444801979905</v>
       </c>
       <c r="K36" t="n">
         <v>0.7760973858799028</v>
@@ -1629,16 +1629,16 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.730520824125831</v>
+        <v>5.730520824125859</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3333296303222881</v>
+        <v>0.3333296303222848</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8290637244215464</v>
+        <v>0.8290637244215473</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5324586169788712</v>
+        <v>0.5324586169788706</v>
       </c>
     </row>
     <row r="38">
@@ -1668,10 +1668,10 @@
         <v>0.3097838756077316</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8644490149762157</v>
+        <v>0.8644490149762196</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5084257313640004</v>
+        <v>0.5084257313639982</v>
       </c>
     </row>
     <row r="39">
@@ -1691,20 +1691,20 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>10.69063360640699</v>
+        <v>5.072597327620704</v>
       </c>
       <c r="I39" t="n">
-        <v>0.05787079694275881</v>
+        <v>0.4070847674856953</v>
       </c>
       <c r="J39" t="n">
-        <v>1.613199608751104</v>
+        <v>0.7298857955274662</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1649967611941539</v>
+        <v>0.6029189649275986</v>
       </c>
     </row>
     <row r="40">
@@ -1724,20 +1724,20 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5.07259732762048</v>
+        <v>10.69063360640709</v>
       </c>
       <c r="I40" t="n">
-        <v>0.407084767485721</v>
+        <v>0.05787079694275654</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7298857955274367</v>
+        <v>1.613199608751117</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6029189649276205</v>
+        <v>0.1649967611941504</v>
       </c>
     </row>
     <row r="41">
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>7.6178787511885</v>
+        <v>7.617878751188542</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1785905851260449</v>
+        <v>0.1785905851260421</v>
       </c>
       <c r="J41" t="n">
-        <v>1.119688419774881</v>
+        <v>1.119688419774887</v>
       </c>
       <c r="K41" t="n">
-        <v>0.3559620826280257</v>
+        <v>0.3559620826280225</v>
       </c>
     </row>
     <row r="42">
@@ -1791,10 +1791,10 @@
         <v>0.001586114996044399</v>
       </c>
       <c r="E42" t="n">
-        <v>227.5486244851176</v>
+        <v>228.2736197954461</v>
       </c>
       <c r="F42" t="n">
-        <v>1.232212952541054e-40</v>
+        <v>8.739141671722778e-41</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -1823,16 +1823,16 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6.59749219459804</v>
+        <v>6.597492194598011</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2523367800566895</v>
+        <v>0.252336780056691</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9614233929918601</v>
+        <v>0.9614233929918503</v>
       </c>
       <c r="K43" t="n">
-        <v>0.4460215874575285</v>
+        <v>0.4460215874575348</v>
       </c>
     </row>
     <row r="44">
@@ -1862,10 +1862,10 @@
         <v>0.5930096712298831</v>
       </c>
       <c r="J44" t="n">
-        <v>0.5267594755698599</v>
+        <v>0.5267594755698617</v>
       </c>
       <c r="K44" t="n">
-        <v>0.7554239038413454</v>
+        <v>0.7554239038413439</v>
       </c>
     </row>
     <row r="45">
@@ -1889,16 +1889,16 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.25717766364951</v>
+        <v>1.257177663649412</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9392757617753829</v>
+        <v>0.9392757617753926</v>
       </c>
       <c r="J45" t="n">
-        <v>0.1753599200162285</v>
+        <v>0.175359920016223</v>
       </c>
       <c r="K45" t="n">
-        <v>0.9711313567618092</v>
+        <v>0.9711313567618111</v>
       </c>
     </row>
     <row r="46">
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>4.442652574775904</v>
+        <v>4.442652574775932</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4875927969112019</v>
+        <v>0.4875927969111983</v>
       </c>
       <c r="J46" t="n">
-        <v>0.6359315700653407</v>
+        <v>0.6359315700653417</v>
       </c>
       <c r="K46" t="n">
-        <v>0.6728329660372366</v>
+        <v>0.6728329660372359</v>
       </c>
     </row>
     <row r="47">
@@ -1951,20 +1951,20 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4.502809546323688</v>
+        <v>6.653162423962202</v>
       </c>
       <c r="I47" t="n">
-        <v>0.479507618470537</v>
+        <v>0.2477389431153512</v>
       </c>
       <c r="J47" t="n">
-        <v>0.6448617109043783</v>
+        <v>0.9699882169327532</v>
       </c>
       <c r="K47" t="n">
-        <v>0.6661012610614507</v>
+        <v>0.4407668350532967</v>
       </c>
     </row>
     <row r="48">
@@ -1984,20 +1984,20 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>6.6531624239623</v>
+        <v>4.502809546323758</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2477389431153431</v>
+        <v>0.4795076184705277</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9699882169327591</v>
+        <v>0.6448617109043788</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4407668350532931</v>
+        <v>0.6661012610614505</v>
       </c>
     </row>
     <row r="49">
@@ -2021,16 +2021,16 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>4.25759732426095</v>
+        <v>4.257597324261006</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5129552338412846</v>
+        <v>0.5129552338412773</v>
       </c>
       <c r="J49" t="n">
-        <v>0.6085159469002741</v>
+        <v>0.608515946900269</v>
       </c>
       <c r="K49" t="n">
-        <v>0.6935630048963749</v>
+        <v>0.693563004896379</v>
       </c>
     </row>
     <row r="50">
@@ -2045,16 +2045,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>502.5080416811143</v>
+        <v>502.5080416811142</v>
       </c>
       <c r="D50" t="n">
-        <v>0.02252737695397429</v>
+        <v>0.02252737695397437</v>
       </c>
       <c r="E50" t="n">
-        <v>256.5781556932396</v>
+        <v>257.2203945505721</v>
       </c>
       <c r="F50" t="n">
-        <v>1.250828366786862e-46</v>
+        <v>9.208721524985714e-47</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
@@ -2083,16 +2083,16 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>7.633365683394067</v>
+        <v>7.633365683393899</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1776327635858215</v>
+        <v>0.1776327635858316</v>
       </c>
       <c r="J51" t="n">
-        <v>1.122111511051239</v>
+        <v>1.122111511051221</v>
       </c>
       <c r="K51" t="n">
-        <v>0.3546997258957229</v>
+        <v>0.3546997258957326</v>
       </c>
     </row>
     <row r="52">
@@ -2116,16 +2116,16 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.052196128399816</v>
+        <v>2.052196128399789</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8418765992101702</v>
+        <v>0.8418765992101742</v>
       </c>
       <c r="J52" t="n">
-        <v>0.2880907246339543</v>
+        <v>0.2880907246339528</v>
       </c>
       <c r="K52" t="n">
-        <v>0.9184183565285013</v>
+        <v>0.918418356528502</v>
       </c>
     </row>
     <row r="53">
@@ -2149,16 +2149,16 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>4.368435571761813</v>
+        <v>4.36843557176187</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4976768388205889</v>
+        <v>0.4976768388205811</v>
       </c>
       <c r="J53" t="n">
-        <v>0.6249264268363663</v>
+        <v>0.6249264268363733</v>
       </c>
       <c r="K53" t="n">
-        <v>0.6811445019888931</v>
+        <v>0.681144501988888</v>
       </c>
     </row>
     <row r="54">
@@ -2182,16 +2182,16 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>5.679258169181383</v>
+        <v>5.679258169181285</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3386895740182437</v>
+        <v>0.3386895740182536</v>
       </c>
       <c r="J54" t="n">
-        <v>0.8212972313842937</v>
+        <v>0.8212972313842819</v>
       </c>
       <c r="K54" t="n">
-        <v>0.537817325146007</v>
+        <v>0.5378173251460154</v>
       </c>
     </row>
     <row r="55">
@@ -2211,20 +2211,20 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>12.73090962274548</v>
+        <v>7.813409377833995</v>
       </c>
       <c r="I55" t="n">
-        <v>0.02603525327685268</v>
+        <v>0.1668232471474025</v>
       </c>
       <c r="J55" t="n">
-        <v>1.955677640722488</v>
+        <v>1.150327820259611</v>
       </c>
       <c r="K55" t="n">
-        <v>0.09329573437837081</v>
+        <v>0.3402572200930096</v>
       </c>
     </row>
     <row r="56">
@@ -2244,20 +2244,20 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>7.813409377833562</v>
+        <v>12.73090962274549</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1668232471474274</v>
+        <v>0.02603525327685259</v>
       </c>
       <c r="J56" t="n">
-        <v>1.150327820259554</v>
+        <v>1.95567764072248</v>
       </c>
       <c r="K56" t="n">
-        <v>0.3402572200930382</v>
+        <v>0.09329573437837201</v>
       </c>
     </row>
     <row r="57">
@@ -2281,16 +2281,16 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>8.013313077894274</v>
+        <v>8.013313077894331</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1555034423803941</v>
+        <v>0.1555034423803908</v>
       </c>
       <c r="J57" t="n">
-        <v>1.181757460885502</v>
+        <v>1.181757460885512</v>
       </c>
       <c r="K57" t="n">
-        <v>0.324724509123351</v>
+        <v>0.3247245091233464</v>
       </c>
     </row>
     <row r="58">
@@ -2305,16 +2305,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>653.5108335461066</v>
+        <v>653.510833546106</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0005056238765954904</v>
+        <v>0.0005056238765955164</v>
       </c>
       <c r="E58" t="n">
-        <v>559.8733930244729</v>
+        <v>560.4677607648529</v>
       </c>
       <c r="F58" t="n">
-        <v>1.817352102835404e-110</v>
+        <v>1.35871569822846e-110</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
@@ -2343,16 +2343,16 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>3.957542511713697</v>
+        <v>3.957542511713669</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2660854196027154</v>
+        <v>0.2660854196027186</v>
       </c>
       <c r="J59" t="n">
-        <v>1.116665944183345</v>
+        <v>1.116665944183344</v>
       </c>
       <c r="K59" t="n">
-        <v>0.3458003016798137</v>
+        <v>0.345800301679814</v>
       </c>
     </row>
     <row r="60">
@@ -2376,16 +2376,16 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>3.577197584008204</v>
+        <v>3.577197584008232</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3108870085491371</v>
+        <v>0.3108870085491341</v>
       </c>
       <c r="J60" t="n">
-        <v>1.006261818647121</v>
+        <v>1.006261818647123</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3931251422753295</v>
+        <v>0.3931251422753287</v>
       </c>
     </row>
     <row r="61">
@@ -2415,10 +2415,10 @@
         <v>0.4417131577325825</v>
       </c>
       <c r="J61" t="n">
-        <v>0.7516986016282797</v>
+        <v>0.7516986016282763</v>
       </c>
       <c r="K61" t="n">
-        <v>0.5237650551180333</v>
+        <v>0.5237650551180351</v>
       </c>
     </row>
     <row r="62">
@@ -2448,10 +2448,10 @@
         <v>0.1610513154581115</v>
       </c>
       <c r="J62" t="n">
-        <v>1.467606351032839</v>
+        <v>1.467606351032834</v>
       </c>
       <c r="K62" t="n">
-        <v>0.2276408598223423</v>
+        <v>0.2276408598223439</v>
       </c>
     </row>
     <row r="63">
@@ -2471,20 +2471,20 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>41.32050264198479</v>
+        <v>4.879364231495487</v>
       </c>
       <c r="I63" t="n">
-        <v>5.591684741097006e-09</v>
+        <v>0.1808468363100113</v>
       </c>
       <c r="J63" t="n">
-        <v>16.6846559630602</v>
+        <v>1.387076561425854</v>
       </c>
       <c r="K63" t="n">
-        <v>6.172504561722808e-09</v>
+        <v>0.2508474853315141</v>
       </c>
     </row>
     <row r="64">
@@ -2504,20 +2504,20 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>4.879364231495487</v>
+        <v>41.32050264198482</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1808468363100113</v>
+        <v>5.591684741096925e-09</v>
       </c>
       <c r="J64" t="n">
-        <v>1.387076561425853</v>
+        <v>16.68465596306019</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2508474853315145</v>
+        <v>6.172504561722868e-09</v>
       </c>
     </row>
     <row r="65">
@@ -2541,16 +2541,16 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>3.938944796437909</v>
+        <v>3.938944796437838</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2681329110154987</v>
+        <v>0.2681329110155066</v>
       </c>
       <c r="J65" t="n">
-        <v>1.111251775580327</v>
+        <v>1.111251775580305</v>
       </c>
       <c r="K65" t="n">
-        <v>0.3479974546114787</v>
+        <v>0.3479974546114877</v>
       </c>
     </row>
   </sheetData>
